--- a/public/templates/sticker-import-template.xlsx
+++ b/public/templates/sticker-import-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac39e7ed8509f1b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{FA43C0CD-9A97-4896-BEBA-0BDEB2213F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22153A26-B417-4B34-AE84-74C74F56D8C5}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{FA43C0CD-9A97-4896-BEBA-0BDEB2213F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34DBCF03-2E61-43E0-B3B4-66EC563C001E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1DD9EBD9-37B7-4B3C-83FC-D8A63E0C6C6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Source Image</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Keyword</t>
+  </si>
+  <si>
+    <t>SKU</t>
   </si>
 </sst>
 </file>
@@ -453,41 +456,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED5F8E78-6D55-4510-8247-50702045D61B}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
